--- a/data/trending_integrated_20261020_11.xlsx
+++ b/data/trending_integrated_20261020_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76150</v>
+        <v>76100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.06%</t>
+          <t>'+17.98%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>88685908950</v>
+        <v>91927558900</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -622,7 +622,7 @@
         <v>72000</v>
       </c>
       <c r="S2" t="n">
-        <v>28000</v>
+        <v>9000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10670</v>
+        <v>10570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.00%</t>
+          <t>'+15.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>130</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>170726963265</v>
+        <v>172706570435</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -711,14 +711,14 @@
         <v>2270</v>
       </c>
       <c r="R3" t="n">
-        <v>405000</v>
+        <v>325000</v>
       </c>
       <c r="S3" t="n">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 및 ESS 사업 부각, 1조원 수주 기대감 및 신고가 경신, 투자경고에도 목표가 상향.</t>
+          <t>HT로보틱스 로봇 사업 성장성 및 수주 잔고 기반의 긍정적 전망. 목표 주가 상향 조정.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '수주잔고']</t>
+          <t>['로봇주', '수주잔고', '목표주가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3925</v>
+        <v>3910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.67%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
         <v>1.66</v>
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>35392454668</v>
+        <v>35662097843</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -803,10 +803,10 @@
         <v>2200</v>
       </c>
       <c r="R4" t="n">
-        <v>-69000</v>
+        <v>-300000</v>
       </c>
       <c r="S4" t="n">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20150</v>
+        <v>20050</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+1.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H5" t="n">
         <v>3.07</v>
@@ -886,7 +886,7 @@
         <v>3.32</v>
       </c>
       <c r="O5" t="n">
-        <v>81248633475</v>
+        <v>81652347425</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -895,7 +895,7 @@
         <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42650</v>
+        <v>42700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>8954093600</v>
+        <v>9245797175</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -987,7 +987,7 @@
         <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-11000</v>
+        <v>-21000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214000</v>
+        <v>213750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.83%</t>
+          <t>'-1.95%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G7" t="n">
-        <v>1224</v>
+        <v>1260</v>
       </c>
       <c r="H7" t="n">
         <v>46.04</v>
@@ -1070,7 +1070,7 @@
         <v>45.99</v>
       </c>
       <c r="O7" t="n">
-        <v>1243210828000</v>
+        <v>1299042715250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1082,20 +1082,20 @@
         <v>356000</v>
       </c>
       <c r="S7" t="n">
-        <v>-501000</v>
+        <v>-408000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 발언과 함께 주가 부양 의지 부족 지적, 공매도 관련 언급.</t>
+          <t>삼성전자 주가에 대한 정치적 비난과 공매도 관련 언급만 존재하며, 객관적인 분석이나 근거는 부족함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이재명 정부', '공매도', '주가 관리']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7300</v>
+        <v>7280</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-2.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>7295678940</v>
+        <v>7519966440</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1174,7 +1174,7 @@
         <v>-176000</v>
       </c>
       <c r="S8" t="n">
-        <v>-19000</v>
+        <v>-15000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14400</v>
+        <v>14380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.68%</t>
+          <t>'-3.81%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,7 +1225,7 @@
         <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
         <v>137</v>
@@ -1254,7 +1254,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>14120476255</v>
+        <v>14560256925</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1266,7 +1266,7 @@
         <v>-56000</v>
       </c>
       <c r="S9" t="n">
-        <v>-39000</v>
+        <v>-37000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17600</v>
+        <v>17580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.83%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H10" t="n">
         <v>27.78</v>
@@ -1346,7 +1346,7 @@
         <v>27.85</v>
       </c>
       <c r="O10" t="n">
-        <v>23945149280</v>
+        <v>25083475255</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1358,7 +1358,7 @@
         <v>-247000</v>
       </c>
       <c r="S10" t="n">
-        <v>-134000</v>
+        <v>-117000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1228000</v>
+        <v>1226000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.84%</t>
+          <t>'-3.99%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="G11" t="n">
-        <v>1578</v>
+        <v>1558</v>
       </c>
       <c r="H11" t="n">
         <v>48.81</v>
@@ -1438,7 +1438,7 @@
         <v>48.82</v>
       </c>
       <c r="O11" t="n">
-        <v>2032685208000</v>
+        <v>2091428858500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1450,20 +1450,20 @@
         <v>-204000</v>
       </c>
       <c r="S11" t="n">
-        <v>-141000</v>
+        <v>-76000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 강한 부정적 전망, 솔리다임 상장 관련 우려 제기.</t>
+          <t>SK하이닉스 주가에 대한 정치적 비난과 함께 주가 하락에 대한 불만 표출이 주를 이루며, 객관적 근거는 미흡함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['이재명 정부', '솔리다임', '주가 하락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2545</v>
+        <v>2535</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.57%</t>
+          <t>'-5.94%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H12" t="n">
         <v>1.14</v>
@@ -1530,7 +1530,7 @@
         <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>25550200562</v>
+        <v>26699101016</v>
       </c>
       <c r="P12" t="n">
         <v>2755</v>
@@ -1539,7 +1539,7 @@
         <v>865</v>
       </c>
       <c r="R12" t="n">
-        <v>297000</v>
+        <v>-12000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1641</v>
+        <v>31700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-6.12%</t>
+          <t>'-6.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>244</v>
+        <v>127</v>
       </c>
       <c r="H13" t="n">
-        <v>1.77</v>
+        <v>12.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1748</v>
+        <v>33950</v>
       </c>
       <c r="K13" t="n">
-        <v>1706</v>
+        <v>33250</v>
       </c>
       <c r="L13" t="n">
-        <v>1895</v>
+        <v>34150</v>
       </c>
       <c r="M13" t="n">
-        <v>1603</v>
+        <v>31300</v>
       </c>
       <c r="N13" t="n">
-        <v>0.83</v>
+        <v>12.81</v>
       </c>
       <c r="O13" t="n">
-        <v>64524279477</v>
+        <v>39349303025</v>
       </c>
       <c r="P13" t="n">
-        <v>2970</v>
+        <v>59300</v>
       </c>
       <c r="Q13" t="n">
-        <v>890</v>
+        <v>22000</v>
       </c>
       <c r="R13" t="n">
-        <v>-457000</v>
+        <v>-137000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시로 인한 급등세 기록. 3일간 코스피 수익률 3위 달성.</t>
+          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재', '급등']</t>
+          <t>['태양광', '공매도', '시장 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31700</v>
+        <v>1609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.63%</t>
+          <t>'-7.95%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="H14" t="n">
-        <v>12.79</v>
+        <v>1.77</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>33950</v>
+        <v>1748</v>
       </c>
       <c r="K14" t="n">
-        <v>33250</v>
+        <v>1706</v>
       </c>
       <c r="L14" t="n">
-        <v>34150</v>
+        <v>1895</v>
       </c>
       <c r="M14" t="n">
-        <v>31300</v>
+        <v>1603</v>
       </c>
       <c r="N14" t="n">
-        <v>12.81</v>
+        <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>37916622650</v>
+        <v>65490602270</v>
       </c>
       <c r="P14" t="n">
-        <v>59300</v>
+        <v>2970</v>
       </c>
       <c r="Q14" t="n">
-        <v>22000</v>
+        <v>890</v>
       </c>
       <c r="R14" t="n">
-        <v>-137000</v>
+        <v>-457000</v>
       </c>
       <c r="S14" t="n">
-        <v>-33000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
+          <t>스페이스X 관련 호재 공시로 인한 급등세 기록. 3일간 코스피 수익률 3위 달성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['태양광', '공매도', '시장 하락']</t>
+          <t>['스페이스X', '호재', '급등']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8870</v>
+        <v>8800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.74%</t>
+          <t>'-9.47%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.15</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
@@ -1806,7 +1806,7 @@
         <v>6.15</v>
       </c>
       <c r="O15" t="n">
-        <v>11876553500</v>
+        <v>12208731160</v>
       </c>
       <c r="P15" t="n">
         <v>14940</v>
@@ -1818,7 +1818,7 @@
         <v>-273000</v>
       </c>
       <c r="S15" t="n">
-        <v>-260000</v>
+        <v>-98000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7970</v>
+        <v>8030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.85%</t>
+          <t>'-10.18%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H16" t="n">
         <v>36.01</v>
@@ -1898,7 +1898,7 @@
         <v>36.39</v>
       </c>
       <c r="O16" t="n">
-        <v>14808388650</v>
+        <v>15024905270</v>
       </c>
       <c r="P16" t="n">
         <v>19150</v>
@@ -1907,10 +1907,10 @@
         <v>3570</v>
       </c>
       <c r="R16" t="n">
-        <v>-110000</v>
+        <v>-36000</v>
       </c>
       <c r="S16" t="n">
-        <v>-8000</v>
+        <v>-5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>70800</v>
+        <v>71800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-13.66%</t>
+          <t>'-12.44%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G17" t="n">
-        <v>516</v>
+        <v>565</v>
       </c>
       <c r="H17" t="n">
         <v>9.380000000000001</v>
@@ -1990,7 +1990,7 @@
         <v>9.44</v>
       </c>
       <c r="O17" t="n">
-        <v>73431729400</v>
+        <v>76657963850</v>
       </c>
       <c r="P17" t="n">
         <v>184000</v>
@@ -2002,20 +2002,20 @@
         <v>-480000</v>
       </c>
       <c r="S17" t="n">
-        <v>-49000</v>
+        <v>-35000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>정치적 발언과 함께 급락에 대한 불만 표출, 공매도 비중 및 기관 매도세 지적.</t>
+          <t>한화시스템 주가 하락에 대한 불만과 공매도 관련 의혹 제기가 있으나, 명확한 근거나 분석은 부족함.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '기관 매도', '주가 하락']</t>
+          <t>['공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">

--- a/data/trending_integrated_20261020_11.xlsx
+++ b/data/trending_integrated_20261020_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76100</v>
+        <v>78500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.98%</t>
+          <t>'+21.71%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -601,7 +601,7 @@
         <v>68000</v>
       </c>
       <c r="L2" t="n">
-        <v>77600</v>
+        <v>78500</v>
       </c>
       <c r="M2" t="n">
         <v>66700</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>91927558900</v>
+        <v>98980133200</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -622,7 +622,7 @@
         <v>72000</v>
       </c>
       <c r="S2" t="n">
-        <v>9000</v>
+        <v>28000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10570</v>
+        <v>10480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.90%</t>
+          <t>'+14.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>172706570435</v>
+        <v>176950568405</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -714,11 +714,11 @@
         <v>325000</v>
       </c>
       <c r="S3" t="n">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HT로보틱스 로봇 사업 성장성 및 수주 잔고 기반의 긍정적 전망. 목표 주가 상향 조정.</t>
+          <t>로봇, ESS, 이차전지 사업 연관성 부각. 7천억 수주잔고 기반 1조원 시총 목표 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇주', '수주잔고', '목표주가']</t>
+          <t>['로봇', 'ESS', '수주잔고']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3910</v>
+        <v>3835</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.27%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>35662097843</v>
+        <v>36637487984</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -806,7 +806,7 @@
         <v>-300000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20050</v>
+        <v>20000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.73%</t>
+          <t>'+1.47%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H5" t="n">
         <v>3.07</v>
@@ -886,7 +886,7 @@
         <v>3.32</v>
       </c>
       <c r="O5" t="n">
-        <v>81652347425</v>
+        <v>82450776550</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42700</v>
+        <v>42750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>9245797175</v>
+        <v>9561899625</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213750</v>
+        <v>216500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.95%</t>
+          <t>'-0.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G7" t="n">
-        <v>1260</v>
+        <v>1308</v>
       </c>
       <c r="H7" t="n">
         <v>46.04</v>
@@ -1070,7 +1070,7 @@
         <v>45.99</v>
       </c>
       <c r="O7" t="n">
-        <v>1299042715250</v>
+        <v>1353138298500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1082,20 +1082,20 @@
         <v>356000</v>
       </c>
       <c r="S7" t="n">
-        <v>-408000</v>
+        <v>-501000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자 주가에 대한 정치적 비난과 공매도 관련 언급만 존재하며, 객관적인 분석이나 근거는 부족함.</t>
+          <t>정부 정책 및 이재명 관련 언급 위주로 부정적 여론 형성. 주가 관리 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['이재명', '정부 정책', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7280</v>
+        <v>7330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.41%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>7519966440</v>
+        <v>7867665165</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1174,7 +1174,7 @@
         <v>-176000</v>
       </c>
       <c r="S8" t="n">
-        <v>-15000</v>
+        <v>-17000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14380</v>
+        <v>1245000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.81%</t>
+          <t>'-2.51%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>525</v>
       </c>
       <c r="G9" t="n">
-        <v>137</v>
+        <v>1592</v>
       </c>
       <c r="H9" t="n">
-        <v>9.779999999999999</v>
+        <v>48.81</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14950</v>
+        <v>1277000</v>
       </c>
       <c r="K9" t="n">
-        <v>14610</v>
+        <v>1265000</v>
       </c>
       <c r="L9" t="n">
-        <v>14940</v>
+        <v>1267000</v>
       </c>
       <c r="M9" t="n">
-        <v>14150</v>
+        <v>1183000</v>
       </c>
       <c r="N9" t="n">
-        <v>9.699999999999999</v>
+        <v>48.82</v>
       </c>
       <c r="O9" t="n">
-        <v>14560256925</v>
+        <v>2177442640000</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>465500</v>
       </c>
       <c r="R9" t="n">
-        <v>-56000</v>
+        <v>-204000</v>
       </c>
       <c r="S9" t="n">
-        <v>-37000</v>
+        <v>-146000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 기대에도 불구하고 주가 하락. 주가 조작 및 공매도 관련 의혹 제기.</t>
+          <t>이재명 정부 경제 정책 비판 및 최태원 회장 책임론 대두. 솔리다임 관련 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['이재명 정부', '최태원', '솔리다임']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17580</v>
+        <v>14510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H10" t="n">
-        <v>27.78</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18300</v>
+        <v>14950</v>
       </c>
       <c r="K10" t="n">
-        <v>18140</v>
+        <v>14610</v>
       </c>
       <c r="L10" t="n">
-        <v>18140</v>
+        <v>14940</v>
       </c>
       <c r="M10" t="n">
-        <v>17280</v>
+        <v>14150</v>
       </c>
       <c r="N10" t="n">
-        <v>27.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>25083475255</v>
+        <v>14978081245</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-247000</v>
+        <v>-56000</v>
       </c>
       <c r="S10" t="n">
-        <v>-117000</v>
+        <v>-39000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
+          <t>3분기 실적 폭증 기대에도 불구하고 주가 하락. 주가 조작 및 공매도 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1226000</v>
+        <v>17710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.99%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>535</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>1558</v>
+        <v>137</v>
       </c>
       <c r="H11" t="n">
-        <v>48.81</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1277000</v>
+        <v>18300</v>
       </c>
       <c r="K11" t="n">
-        <v>1265000</v>
+        <v>18140</v>
       </c>
       <c r="L11" t="n">
-        <v>1267000</v>
+        <v>18140</v>
       </c>
       <c r="M11" t="n">
-        <v>1183000</v>
+        <v>17280</v>
       </c>
       <c r="N11" t="n">
-        <v>48.82</v>
+        <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2091428858500</v>
+        <v>25885756545</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>465500</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>-204000</v>
+        <v>-247000</v>
       </c>
       <c r="S11" t="n">
-        <v>-76000</v>
+        <v>-134000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가에 대한 정치적 비난과 함께 주가 하락에 대한 불만 표출이 주를 이루며, 객관적 근거는 미흡함.</t>
+          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,20 +1463,20 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2535</v>
+        <v>2555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.94%</t>
+          <t>'-5.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H12" t="n">
         <v>1.14</v>
@@ -1530,7 +1530,7 @@
         <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>26699101016</v>
+        <v>26971738916</v>
       </c>
       <c r="P12" t="n">
         <v>2755</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31700</v>
+        <v>31900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-6.63%</t>
+          <t>'-6.04%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H13" t="n">
         <v>12.79</v>
@@ -1622,7 +1622,7 @@
         <v>12.81</v>
       </c>
       <c r="O13" t="n">
-        <v>39349303025</v>
+        <v>40813666150</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1634,7 +1634,7 @@
         <v>-137000</v>
       </c>
       <c r="S13" t="n">
-        <v>-12000</v>
+        <v>-35000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1609</v>
+        <v>1591</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.95%</t>
+          <t>'-8.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="H14" t="n">
         <v>1.77</v>
@@ -1708,13 +1708,13 @@
         <v>1895</v>
       </c>
       <c r="M14" t="n">
-        <v>1603</v>
+        <v>1585</v>
       </c>
       <c r="N14" t="n">
         <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>65490602270</v>
+        <v>66417104061</v>
       </c>
       <c r="P14" t="n">
         <v>2970</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시로 인한 급등세 기록. 3일간 코스피 수익률 3위 달성.</t>
+          <t>스페이스X 관련 호재 공시와 함께 코스피 수익률 3위 달성. 2~3연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재', '급등']</t>
+          <t>['스페이스X', '호재', '수익률']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8800</v>
+        <v>8110</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.47%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.15</v>
+        <v>-0.38</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>36.01</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9720</v>
+        <v>8940</v>
       </c>
       <c r="K15" t="n">
-        <v>9930</v>
+        <v>9000</v>
       </c>
       <c r="L15" t="n">
-        <v>9930</v>
+        <v>9010</v>
       </c>
       <c r="M15" t="n">
-        <v>8750</v>
+        <v>7750</v>
       </c>
       <c r="N15" t="n">
-        <v>6.15</v>
+        <v>36.39</v>
       </c>
       <c r="O15" t="n">
-        <v>12208731160</v>
+        <v>15336085720</v>
       </c>
       <c r="P15" t="n">
-        <v>14940</v>
+        <v>19150</v>
       </c>
       <c r="Q15" t="n">
-        <v>5390</v>
+        <v>3570</v>
       </c>
       <c r="R15" t="n">
-        <v>-273000</v>
+        <v>-36000</v>
       </c>
       <c r="S15" t="n">
-        <v>-98000</v>
+        <v>-8000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>테슬라 관련 기대감 있으나, 주가 하락 및 고평가 부담에 대한 언급.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['테슬라', '주가 하락', '공매도']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,99 +1844,99 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8030</v>
+        <v>8810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.18%</t>
+          <t>'-9.36%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="H16" t="n">
-        <v>36.01</v>
+        <v>6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8940</v>
+        <v>9720</v>
       </c>
       <c r="K16" t="n">
-        <v>9000</v>
+        <v>9930</v>
       </c>
       <c r="L16" t="n">
-        <v>9010</v>
+        <v>9930</v>
       </c>
       <c r="M16" t="n">
-        <v>7750</v>
+        <v>8750</v>
       </c>
       <c r="N16" t="n">
-        <v>36.39</v>
+        <v>6.15</v>
       </c>
       <c r="O16" t="n">
-        <v>15024905270</v>
+        <v>12538424420</v>
       </c>
       <c r="P16" t="n">
-        <v>19150</v>
+        <v>14940</v>
       </c>
       <c r="Q16" t="n">
-        <v>3570</v>
+        <v>5390</v>
       </c>
       <c r="R16" t="n">
-        <v>-36000</v>
+        <v>-273000</v>
       </c>
       <c r="S16" t="n">
-        <v>-5000</v>
+        <v>-244000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>시초 급등 후 하락세. 테슬라 관련 기대감 있으나 지수 및 공매도 부담으로 인한 변동성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['테슬라', '공매도', '변동성']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>71800</v>
+        <v>72450</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-12.44%</t>
+          <t>'-11.65%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G17" t="n">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="H17" t="n">
         <v>9.380000000000001</v>
@@ -1990,7 +1990,7 @@
         <v>9.44</v>
       </c>
       <c r="O17" t="n">
-        <v>76657963850</v>
+        <v>78889006300</v>
       </c>
       <c r="P17" t="n">
         <v>184000</v>
@@ -2002,7 +2002,7 @@
         <v>-480000</v>
       </c>
       <c r="S17" t="n">
-        <v>-35000</v>
+        <v>-49000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261020_11.xlsx
+++ b/data/trending_integrated_20261020_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78500</v>
+        <v>77700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.71%</t>
+          <t>'+20.47%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -601,7 +601,7 @@
         <v>68000</v>
       </c>
       <c r="L2" t="n">
-        <v>78500</v>
+        <v>79300</v>
       </c>
       <c r="M2" t="n">
         <v>66700</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>98980133200</v>
+        <v>104840496000</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10480</v>
+        <v>10450</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.91%</t>
+          <t>'+14.58%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>176950568405</v>
+        <v>181234783430</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 사업 연관성 부각. 7천억 수주잔고 기반 1조원 시총 목표 제시.</t>
+          <t>로봇 사업 성장성, 수주 잔고 기반 긍정적 전망, 신고가 및 1조 시총 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '수주잔고']</t>
+          <t>['로봇', '수주 잔고', '신고가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3835</v>
+        <v>3820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+1.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
         <v>23</v>
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>36637487984</v>
+        <v>37472102660</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -854,10 +854,10 @@
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
         <v>115</v>
@@ -886,7 +886,7 @@
         <v>3.32</v>
       </c>
       <c r="O5" t="n">
-        <v>82450776550</v>
+        <v>82753289245</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42750</v>
+        <v>42600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>743</v>
+        <v>771</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>9561899625</v>
+        <v>9750285575</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216500</v>
+        <v>214250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.69%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G7" t="n">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="H7" t="n">
         <v>46.04</v>
@@ -1070,7 +1070,7 @@
         <v>45.99</v>
       </c>
       <c r="O7" t="n">
-        <v>1353138298500</v>
+        <v>1389621546000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정부 정책 및 이재명 관련 언급 위주로 부정적 여론 형성. 주가 관리 의혹 제기.</t>
+          <t>정치적 이슈에 따른 부정적 언급 다수, 주가 관리 부재 비판.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이재명', '정부 정책', '공매도']</t>
+          <t>['정치', '주가 관리', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7330</v>
+        <v>7310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
         <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>7867665165</v>
+        <v>8069321315</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1245000</v>
+        <v>14470</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.51%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>525</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>1592</v>
+        <v>132</v>
       </c>
       <c r="H9" t="n">
-        <v>48.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1277000</v>
+        <v>14950</v>
       </c>
       <c r="K9" t="n">
-        <v>1265000</v>
+        <v>14610</v>
       </c>
       <c r="L9" t="n">
-        <v>1267000</v>
+        <v>14940</v>
       </c>
       <c r="M9" t="n">
-        <v>1183000</v>
+        <v>14150</v>
       </c>
       <c r="N9" t="n">
-        <v>48.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>2177442640000</v>
+        <v>15323757635</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>465500</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-204000</v>
+        <v>-56000</v>
       </c>
       <c r="S9" t="n">
-        <v>-146000</v>
+        <v>-39000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재명 정부 경제 정책 비판 및 최태원 회장 책임론 대두. 솔리다임 관련 우려.</t>
+          <t>3분기 실적 폭증 기대에도 불구하고 주가 하락. 주가 조작 및 공매도 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명 정부', '최태원', '솔리다임']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14510</v>
+        <v>17660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-3.50%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H10" t="n">
-        <v>9.779999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14950</v>
+        <v>18300</v>
       </c>
       <c r="K10" t="n">
-        <v>14610</v>
+        <v>18140</v>
       </c>
       <c r="L10" t="n">
-        <v>14940</v>
+        <v>18140</v>
       </c>
       <c r="M10" t="n">
-        <v>14150</v>
+        <v>17280</v>
       </c>
       <c r="N10" t="n">
-        <v>9.699999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="O10" t="n">
-        <v>14978081245</v>
+        <v>26350115485</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>-56000</v>
+        <v>-247000</v>
       </c>
       <c r="S10" t="n">
-        <v>-39000</v>
+        <v>-134000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 기대에도 불구하고 주가 하락. 주가 조작 및 공매도 관련 의혹 제기.</t>
+          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17710</v>
+        <v>1232000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-3.52%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>518</v>
       </c>
       <c r="G11" t="n">
-        <v>137</v>
+        <v>1630</v>
       </c>
       <c r="H11" t="n">
-        <v>27.78</v>
+        <v>48.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,60 +1423,60 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18300</v>
+        <v>1277000</v>
       </c>
       <c r="K11" t="n">
-        <v>18140</v>
+        <v>1265000</v>
       </c>
       <c r="L11" t="n">
-        <v>18140</v>
+        <v>1267000</v>
       </c>
       <c r="M11" t="n">
-        <v>17280</v>
+        <v>1183000</v>
       </c>
       <c r="N11" t="n">
-        <v>27.85</v>
+        <v>48.82</v>
       </c>
       <c r="O11" t="n">
-        <v>25885756545</v>
+        <v>2237154669000</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>465500</v>
       </c>
       <c r="R11" t="n">
-        <v>-247000</v>
+        <v>-204000</v>
       </c>
       <c r="S11" t="n">
-        <v>-134000</v>
+        <v>-146000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
+          <t>정치적 요인 및 솔리다임 상장 관련 부정적 전망, 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
+          <t>['솔리다임', '정치', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2555</v>
+        <v>2565</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.19%</t>
+          <t>'-4.82%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H12" t="n">
         <v>1.14</v>
@@ -1530,7 +1530,7 @@
         <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>26971738916</v>
+        <v>27372011616</v>
       </c>
       <c r="P12" t="n">
         <v>2755</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31900</v>
+        <v>31650</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-6.04%</t>
+          <t>'-6.77%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H13" t="n">
         <v>12.79</v>
@@ -1622,7 +1622,7 @@
         <v>12.81</v>
       </c>
       <c r="O13" t="n">
-        <v>40813666150</v>
+        <v>42127260300</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1591</v>
+        <v>1608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.98%</t>
+          <t>'-8.01%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="F14" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="H14" t="n">
         <v>1.77</v>
@@ -1714,7 +1714,7 @@
         <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>66417104061</v>
+        <v>66809475855</v>
       </c>
       <c r="P14" t="n">
         <v>2970</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8110</v>
+        <v>8080</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.28%</t>
+          <t>'-9.62%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.38</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H15" t="n">
         <v>36.01</v>
@@ -1806,7 +1806,7 @@
         <v>36.39</v>
       </c>
       <c r="O15" t="n">
-        <v>15336085720</v>
+        <v>15605809100</v>
       </c>
       <c r="P15" t="n">
         <v>19150</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8810</v>
+        <v>8760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-9.36%</t>
+          <t>'-9.88%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
         <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
@@ -1892,13 +1892,13 @@
         <v>9930</v>
       </c>
       <c r="M16" t="n">
-        <v>8750</v>
+        <v>8740</v>
       </c>
       <c r="N16" t="n">
         <v>6.15</v>
       </c>
       <c r="O16" t="n">
-        <v>12538424420</v>
+        <v>13003711675</v>
       </c>
       <c r="P16" t="n">
         <v>14940</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>시초 급등 후 하락세. 테슬라 관련 기대감 있으나 지수 및 공매도 부담으로 인한 변동성.</t>
+          <t>주가 급등 후 하락 가능성 언급, 공매도 세력 개입 및 밸류 부담 지적.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['테슬라', '공매도', '변동성']</t>
+          <t>['공매도', '밸류 부담', '테슬라']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>72450</v>
+        <v>72400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.65%</t>
+          <t>'-11.71%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F17" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G17" t="n">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="H17" t="n">
         <v>9.380000000000001</v>
@@ -1990,7 +1990,7 @@
         <v>9.44</v>
       </c>
       <c r="O17" t="n">
-        <v>78889006300</v>
+        <v>80707937200</v>
       </c>
       <c r="P17" t="n">
         <v>184000</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>한화시스템 주가 하락에 대한 불만과 공매도 관련 의혹 제기가 있으나, 명확한 근거나 분석은 부족함.</t>
+          <t>정치적 이슈 및 공매도에 따른 주가 급락, 금감원 신고 고려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도']</t>
+          <t>['공매도', '정치', '주가 급락']</t>
         </is>
       </c>
       <c r="X17" t="n">

--- a/data/trending_integrated_20261020_11.xlsx
+++ b/data/trending_integrated_20261020_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77700</v>
+        <v>77900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.47%</t>
+          <t>'+20.78%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>104840496000</v>
+        <v>107223232600</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10450</v>
+        <v>10405</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.58%</t>
+          <t>'+14.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>181234783430</v>
+        <v>182854825505</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 사업 성장성, 수주 잔고 기반 긍정적 전망, 신고가 및 1조 시총 기대.</t>
+          <t>로봇, ESS, 이차전지 사업 연관성 부각. 7천억 수주잔고 및 1조 이상 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '수주 잔고', '신고가']</t>
+          <t>['로봇', '수주', 'ESS']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3820</v>
+        <v>3825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.87%</t>
+          <t>'+2.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
         <v>23</v>
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>37472102660</v>
+        <v>37708566100</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -860,7 +860,7 @@
         <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H5" t="n">
         <v>3.07</v>
@@ -886,7 +886,7 @@
         <v>3.32</v>
       </c>
       <c r="O5" t="n">
-        <v>82753289245</v>
+        <v>83177484420</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -946,13 +946,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F6" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G6" t="n">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>9750285575</v>
+        <v>9966630875</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G7" t="n">
-        <v>1305</v>
+        <v>1366</v>
       </c>
       <c r="H7" t="n">
         <v>46.04</v>
@@ -1070,7 +1070,7 @@
         <v>45.99</v>
       </c>
       <c r="O7" t="n">
-        <v>1389621546000</v>
+        <v>1408750939000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈에 따른 부정적 언급 다수, 주가 관리 부재 비판.</t>
+          <t>정치적 이슈와 연관된 부정적 언급 다수. 금감원 공매도 잠정 중단 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정치', '주가 관리', '공매도']</t>
+          <t>['정치', '공매도', '증시']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7310</v>
+        <v>7320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>8069321315</v>
+        <v>8419060785</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1222,7 +1222,7 @@
         <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
         <v>42</v>
@@ -1254,7 +1254,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>15323757635</v>
+        <v>15526032905</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17660</v>
+        <v>1234000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.50%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>521</v>
       </c>
       <c r="G10" t="n">
-        <v>137</v>
+        <v>1575</v>
       </c>
       <c r="H10" t="n">
-        <v>27.78</v>
+        <v>48.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18300</v>
+        <v>1277000</v>
       </c>
       <c r="K10" t="n">
-        <v>18140</v>
+        <v>1265000</v>
       </c>
       <c r="L10" t="n">
-        <v>18140</v>
+        <v>1267000</v>
       </c>
       <c r="M10" t="n">
-        <v>17280</v>
+        <v>1183000</v>
       </c>
       <c r="N10" t="n">
-        <v>27.85</v>
+        <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>26350115485</v>
+        <v>2296403554000</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>17210</v>
+        <v>465500</v>
       </c>
       <c r="R10" t="n">
-        <v>-247000</v>
+        <v>-204000</v>
       </c>
       <c r="S10" t="n">
-        <v>-134000</v>
+        <v>-146000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
+          <t>정치적 이슈와 연관된 부정적 언급 다수. 솔리다임 상장 관련 불확실성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
+          <t>['정치', '솔리다임', '하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1232000</v>
+        <v>17640</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.52%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>518</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>1630</v>
+        <v>138</v>
       </c>
       <c r="H11" t="n">
-        <v>48.81</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,60 +1423,60 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1277000</v>
+        <v>18300</v>
       </c>
       <c r="K11" t="n">
-        <v>1265000</v>
+        <v>18140</v>
       </c>
       <c r="L11" t="n">
-        <v>1267000</v>
+        <v>18140</v>
       </c>
       <c r="M11" t="n">
-        <v>1183000</v>
+        <v>17280</v>
       </c>
       <c r="N11" t="n">
-        <v>48.82</v>
+        <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2237154669000</v>
+        <v>26881264920</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>465500</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>-204000</v>
+        <v>-247000</v>
       </c>
       <c r="S11" t="n">
-        <v>-146000</v>
+        <v>-134000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 요인 및 솔리다임 상장 관련 부정적 전망, 주가 하락 우려.</t>
+          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['솔리다임', '정치', '주가 하락']</t>
+          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2565</v>
+        <v>2560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.82%</t>
+          <t>'-5.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H12" t="n">
         <v>1.14</v>
@@ -1530,7 +1530,7 @@
         <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>27372011616</v>
+        <v>27487773121</v>
       </c>
       <c r="P12" t="n">
         <v>2755</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31650</v>
+        <v>31550</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-6.77%</t>
+          <t>'-7.07%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="H13" t="n">
         <v>12.79</v>
@@ -1622,7 +1622,7 @@
         <v>12.81</v>
       </c>
       <c r="O13" t="n">
-        <v>42127260300</v>
+        <v>43577988000</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1608</v>
+        <v>1595</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.01%</t>
+          <t>'-8.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="H14" t="n">
         <v>1.77</v>
@@ -1714,7 +1714,7 @@
         <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>66809475855</v>
+        <v>67094560789</v>
       </c>
       <c r="P14" t="n">
         <v>2970</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시와 함께 코스피 수익률 3위 달성. 2~3연상 기대감 형성.</t>
+          <t>스페이스X 관련 호재 공시로 인한 급등세 기록. 3일간 코스피 수익률 3위 달성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재', '수익률']</t>
+          <t>['스페이스X', '호재', '급등']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8080</v>
+        <v>8010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.62%</t>
+          <t>'-10.40%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.38</v>
       </c>
       <c r="E15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
         <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H15" t="n">
         <v>36.01</v>
@@ -1806,7 +1806,7 @@
         <v>36.39</v>
       </c>
       <c r="O15" t="n">
-        <v>15605809100</v>
+        <v>15832809920</v>
       </c>
       <c r="P15" t="n">
         <v>19150</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8760</v>
+        <v>8700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-9.88%</t>
+          <t>'-10.49%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
         <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
@@ -1892,13 +1892,13 @@
         <v>9930</v>
       </c>
       <c r="M16" t="n">
-        <v>8740</v>
+        <v>8690</v>
       </c>
       <c r="N16" t="n">
         <v>6.15</v>
       </c>
       <c r="O16" t="n">
-        <v>13003711675</v>
+        <v>13536413085</v>
       </c>
       <c r="P16" t="n">
         <v>14940</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 급등 후 하락 가능성 언급, 공매도 세력 개입 및 밸류 부담 지적.</t>
+          <t>주주환원 정책 부재에 대한 지적. 테슬라 관련 언급 및 공매도 세력에 대한 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '밸류 부담', '테슬라']</t>
+          <t>['주주환원', '공매도', '테슬라']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>72400</v>
+        <v>72500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.71%</t>
+          <t>'-11.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G17" t="n">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="H17" t="n">
         <v>9.380000000000001</v>
@@ -1990,7 +1990,7 @@
         <v>9.44</v>
       </c>
       <c r="O17" t="n">
-        <v>80707937200</v>
+        <v>82108993750</v>
       </c>
       <c r="P17" t="n">
         <v>184000</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 공매도에 따른 주가 급락, 금감원 신고 고려.</t>
+          <t>정치적 이슈와 연관된 부정적 언급 다수. 공매도 비율 및 급락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '정치', '주가 급락']</t>
+          <t>['정치', '공매도', '하락']</t>
         </is>
       </c>
       <c r="X17" t="n">

--- a/data/trending_integrated_20261020_11.xlsx
+++ b/data/trending_integrated_20261020_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77900</v>
+        <v>78000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.78%</t>
+          <t>'+20.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>107223232600</v>
+        <v>109204154300</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10405</v>
+        <v>10330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.09%</t>
+          <t>'+13.27%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G3" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>182854825505</v>
+        <v>187769759035</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇, ESS, 이차전지 사업 연관성 부각. 7천억 수주잔고 및 1조 이상 수주 가능성 언급.</t>
+          <t>ESS, 로봇, 이차전지 사업 관련 언급과 함께 수주 잔고 7천억, 1조 클럽 가능성 등 구체적인 팩트 기반 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '수주', 'ESS']</t>
+          <t>['ESS', '로봇', '수주잔고']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3825</v>
+        <v>3830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.00%</t>
+          <t>'+2.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
         <v>23</v>
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>37708566100</v>
+        <v>37987396745</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -860,7 +860,7 @@
         <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H5" t="n">
         <v>3.07</v>
@@ -886,7 +886,7 @@
         <v>3.32</v>
       </c>
       <c r="O5" t="n">
-        <v>83177484420</v>
+        <v>83609288420</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42600</v>
+        <v>42750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.81%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>92</v>
       </c>
       <c r="G6" t="n">
-        <v>787</v>
+        <v>818</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>9966630875</v>
+        <v>10196155625</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 발표 기대감 속 매수세 유입, 담관암 FDA 승인 이슈 및 신뢰 회복 필요성 언급.</t>
+          <t>C1 발표 및 FDA 승인 관련 기대감이 있으나, 주가 상승 여부에 대한 불확실성 및 시장 신뢰 회복 필요성 등 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1', 'FDA 승인', '매수세']</t>
+          <t>['C1', 'FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214250</v>
+        <v>215000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="G7" t="n">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="H7" t="n">
         <v>46.04</v>
@@ -1070,7 +1070,7 @@
         <v>45.99</v>
       </c>
       <c r="O7" t="n">
-        <v>1408750939000</v>
+        <v>1452929616750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 언급 다수. 금감원 공매도 잠정 중단 언급.</t>
+          <t>정치적 발언이 주를 이루며 주가 관련 객관적 근거는 부재함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정치', '공매도', '증시']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1136,7 +1136,7 @@
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>8419060785</v>
+        <v>8561618920</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14470</v>
+        <v>1241000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>525</v>
       </c>
       <c r="G9" t="n">
-        <v>132</v>
+        <v>1547</v>
       </c>
       <c r="H9" t="n">
-        <v>9.779999999999999</v>
+        <v>48.81</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14950</v>
+        <v>1277000</v>
       </c>
       <c r="K9" t="n">
-        <v>14610</v>
+        <v>1265000</v>
       </c>
       <c r="L9" t="n">
-        <v>14940</v>
+        <v>1267000</v>
       </c>
       <c r="M9" t="n">
-        <v>14150</v>
+        <v>1183000</v>
       </c>
       <c r="N9" t="n">
-        <v>9.699999999999999</v>
+        <v>48.82</v>
       </c>
       <c r="O9" t="n">
-        <v>15526032905</v>
+        <v>2353994411000</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>465500</v>
       </c>
       <c r="R9" t="n">
-        <v>-56000</v>
+        <v>-204000</v>
       </c>
       <c r="S9" t="n">
-        <v>-39000</v>
+        <v>-146000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 기대에도 불구하고 주가 하락. 주가 조작 및 공매도 관련 의혹 제기.</t>
+          <t>정치적 이슈 및 특정 인물에 대한 부정적 언급이 많으며, 솔리다임 상장 관련 언급이 있으나 구체적 분석은 부족함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['솔리다임']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1234000</v>
+        <v>14520</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.37%</t>
+          <t>'-2.88%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
-        <v>521</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>1575</v>
+        <v>133</v>
       </c>
       <c r="H10" t="n">
-        <v>48.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1277000</v>
+        <v>14950</v>
       </c>
       <c r="K10" t="n">
-        <v>1265000</v>
+        <v>14610</v>
       </c>
       <c r="L10" t="n">
-        <v>1267000</v>
+        <v>14940</v>
       </c>
       <c r="M10" t="n">
-        <v>1183000</v>
+        <v>14150</v>
       </c>
       <c r="N10" t="n">
-        <v>48.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>2296403554000</v>
+        <v>15750570260</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>465500</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-204000</v>
+        <v>-56000</v>
       </c>
       <c r="S10" t="n">
-        <v>-146000</v>
+        <v>-39000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 언급 다수. 솔리다임 상장 관련 불확실성.</t>
+          <t>3분기 실적 폭증 기대에도 불구하고 주가 하락. 주가 조작 및 공매도 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치', '솔리다임', '하락']</t>
+          <t>['실적', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17640</v>
+        <v>17650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H11" t="n">
         <v>27.78</v>
@@ -1438,7 +1438,7 @@
         <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>26881264920</v>
+        <v>27929332070</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2560</v>
+        <v>2585</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.01%</t>
+          <t>'-4.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H12" t="n">
         <v>1.14</v>
@@ -1530,7 +1530,7 @@
         <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>27487773121</v>
+        <v>27797028119</v>
       </c>
       <c r="P12" t="n">
         <v>2755</v>
@@ -1590,13 +1590,13 @@
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H13" t="n">
         <v>12.79</v>
@@ -1622,7 +1622,7 @@
         <v>12.81</v>
       </c>
       <c r="O13" t="n">
-        <v>43577988000</v>
+        <v>44626342800</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.75%</t>
+          <t>'-8.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G14" t="n">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="H14" t="n">
         <v>1.77</v>
@@ -1714,7 +1714,7 @@
         <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>67094560789</v>
+        <v>67343068345</v>
       </c>
       <c r="P14" t="n">
         <v>2970</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8010</v>
+        <v>8020</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-10.40%</t>
+          <t>'-10.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.38</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" t="n">
         <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H15" t="n">
         <v>36.01</v>
@@ -1806,7 +1806,7 @@
         <v>36.39</v>
       </c>
       <c r="O15" t="n">
-        <v>15832809920</v>
+        <v>15888575390</v>
       </c>
       <c r="P15" t="n">
         <v>19150</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8700</v>
+        <v>8680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.49%</t>
+          <t>'-10.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
@@ -1892,13 +1892,13 @@
         <v>9930</v>
       </c>
       <c r="M16" t="n">
-        <v>8690</v>
+        <v>8660</v>
       </c>
       <c r="N16" t="n">
         <v>6.15</v>
       </c>
       <c r="O16" t="n">
-        <v>13536413085</v>
+        <v>13967026990</v>
       </c>
       <c r="P16" t="n">
         <v>14940</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주주환원 정책 부재에 대한 지적. 테슬라 관련 언급 및 공매도 세력에 대한 우려.</t>
+          <t>개별 종목의 주가 흐름에 대한 언급과 함께 테슬라 관련 언급이 있으나, 구체적인 팩트 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주환원', '공매도', '테슬라']</t>
+          <t>['테슬라']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>72500</v>
+        <v>72700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.59%</t>
+          <t>'-11.34%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F17" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G17" t="n">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="H17" t="n">
         <v>9.380000000000001</v>
@@ -1990,7 +1990,7 @@
         <v>9.44</v>
       </c>
       <c r="O17" t="n">
-        <v>82108993750</v>
+        <v>83850311250</v>
       </c>
       <c r="P17" t="n">
         <v>184000</v>
